--- a/data/Overall Market Penetration by Distance.xlsx
+++ b/data/Overall Market Penetration by Distance.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +29,18 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +63,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -425,53 +449,124 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Distance Range</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Penetration %</t>
         </is>
       </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Customer Count</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0-24 mi</t>
-        </is>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>0-49 mi</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>293</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>25-49 mi</t>
-        </is>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>50-99 mi</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>558</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>50-99 mi</t>
-        </is>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>100-149 mi</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>490</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>100-199 mi</t>
-        </is>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>150-199 mi</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>146</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>200-499 mi</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>200-249 mi</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>250-299 mi</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>300+ mi</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Source: Cedar Crest Weekly Sales Database - April2025-March2026.xlsx, 'Summary - All Weeks' tab, filtered to customers with Weeks Ordered &gt;= 3 (1,523 of 1,730 total customers). Distance = 'Miles to Country Dairy' column. Base for % = 1,502 customers with a mapped ZIP/distance (21 of the 1,523 eligible customers have no ZIP geocode match and are excluded). Bands are even 50-mile increments; the single customer beyond 300 mi (a distributor, ~684 mi) falls in the open-ended 300+ mi band.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:C10"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>